--- a/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:03</t>
+    <t xml:space="preserve">2026-09-10 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:15</t>
+    <t xml:space="preserve">2026-09-12 22:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_depmen_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:27</t>
+    <t xml:space="preserve">2026-09-23 23:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
